--- a/data/instance_micro_P2_M3_T2.xlsx
+++ b/data/instance_micro_P2_M3_T2.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Custos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demanda_Cor" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Estoque_Cor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="De_Para_Cores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +23,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,27 +428,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -514,22 +509,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01/2024</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>02/2024</t>
         </is>
@@ -586,17 +581,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>12/2023</t>
         </is>
@@ -647,17 +642,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CUSTO_UNITARIO</t>
         </is>
@@ -708,22 +703,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -760,6 +755,516 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>QUANTIDADE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PRAZO_ENTREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>23028.01588991644</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>45315</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4127.447685846103</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>45298</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>25455.74268783761</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>45333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4562.583539575213</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>45336</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18403.23504490685</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9835.310734746616</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>45293</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16070.54589416968</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8588.642820703875</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>45327</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ESTOQUE_INICIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>24241.87928887703</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4345.015612710658</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17236.89046953827</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9211.976777725245</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1.617143233861726</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9887380372072279</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.204333716913712</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8403640235763261</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1.155727878308496</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.550397653003374</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.748389702092802</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.081217568545262</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.523743255962463</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1.497276284888048</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.671093546532952</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.353111793929341</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1.206644309214699</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.647498286124038</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.330369100986994</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9559251470939183</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0.8218770092292937</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.780104609902249</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.9403906366500254</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.335548228511918</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
